--- a/backend/data/uploads/MES/2026-07-20_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-20_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9AADDE06-321E-4FED-92B7-84207D94DE37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2964A3B4-EA0C-4AF0-B6B8-B55F01870E8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{1281134C-A36D-48E9-9AEC-B04ECC62F58C}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{70AC1E0C-6BED-4144-8F9B-22CC453D9A75}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EABA0D77-28F8-4041-B6A0-CDEDC13497AD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBF780B4-3B76-4F74-B7B5-EBFB4F0FFADD}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/MES/2026-07-20_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-20_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2964A3B4-EA0C-4AF0-B6B8-B55F01870E8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{050C44C6-18F4-486A-9F21-1A74FBE7E3C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{70AC1E0C-6BED-4144-8F9B-22CC453D9A75}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{8C000E1B-2E7B-42EC-A34C-0F6BB6E1726C}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBF780B4-3B76-4F74-B7B5-EBFB4F0FFADD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ACF50E1-477C-405E-85DF-D1922A94877A}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/MES/2026-07-20_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-20_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{050C44C6-18F4-486A-9F21-1A74FBE7E3C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C3D37AEE-DE7F-454C-9E67-5E95F8D1F7FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{8C000E1B-2E7B-42EC-A34C-0F6BB6E1726C}"/>
+    <workbookView xWindow="-30240" yWindow="8376" windowWidth="23040" windowHeight="12012" xr2:uid="{16292BAB-27A9-47D1-9663-19CD76347980}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ACF50E1-477C-405E-85DF-D1922A94877A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{853C640E-7A14-4AC1-B154-9C3C6C8CF980}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
